--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -66,7 +66,7 @@
     <x:t>Amateur</x:t>
   </x:si>
   <x:si>
-    <x:t>EDISSA  ABASTAS AMANTE</x:t>
+    <x:t>EDISSA ABASTAS AMANTE</x:t>
   </x:si>
   <x:si>
     <x:t>Manimpis, City Of San Fernando (Capital), Pampanga</x:t>
@@ -114,7 +114,7 @@
     <x:t>61-6-2025-1054</x:t>
   </x:si>
   <x:si>
-    <x:t>ANGELICA  VERGARA PANCHITO</x:t>
+    <x:t>ANGELICA VERGARA PANCHITO</x:t>
   </x:si>
   <x:si>
     <x:t>TEMP-ROIII-1007-25</x:t>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -87,19 +87,19 @@
     <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
   </x:si>
   <x:si>
+    <x:t>TEMP-ROIII-1018-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANUELITO TOLENTINO</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEMP-ROIII-1003-25</x:t>
   </x:si>
   <x:si>
     <x:t>61-6-2025-1003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1018-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANUELITO TOLENTINO</x:t>
   </x:si>
   <x:si>
     <x:t>Radiotelegraphy</x:t>
@@ -1054,22 +1054,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>45825.0450347222</x:v>
+        <x:v>45826.3053472222</x:v>
       </x:c>
       <x:c r="I7" s="12">
-        <x:v>45825.0450578704</x:v>
+        <x:v>45826.3053703704</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1546810</x:v>
+        <x:v>1434444</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>45825.0561574074</x:v>
+        <x:v>45826.3117939815</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
@@ -1085,28 +1085,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>45826.3053472222</x:v>
+        <x:v>45825.0450347222</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>45826.3053703704</x:v>
+        <x:v>45825.0450578704</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1434444</x:v>
+        <x:v>1546810</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>45826.3117939815</x:v>
+        <x:v>45825.0561574074</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1178,7 +1178,7 @@
         <x:v>45825.2871759259</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -1214,7 +1214,7 @@
         <x:v>45826.3168865741</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="June 2025" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -154,7 +118,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -181,12 +145,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -194,6 +152,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -208,13 +187,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -259,12 +231,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -276,14 +248,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -465,7 +437,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -476,176 +448,194 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -909,366 +899,342 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45832.3271759259</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>45832.3271990741</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>16854</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45832.3384259259</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
         <x:v>45826.3053472222</x:v>
       </x:c>
-      <x:c r="I7" s="12">
+      <x:c r="I7" s="17">
         <x:v>45826.3053703704</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="16" t="n">
         <x:v>1434444</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K7" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="17">
         <x:v>45826.3117939815</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="16" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s"/>
+      <x:c r="E8" s="19" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="20">
         <x:v>45825.0450347222</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="20">
         <x:v>45825.0450578704</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="n">
+      <x:c r="J8" s="19" t="n">
         <x:v>1546810</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="21" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="18">
+      <x:c r="L8" s="20">
         <x:v>45825.0561574074</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="19" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
+      <x:c r="B9" s="19" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s"/>
+      <x:c r="E9" s="19" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
         <x:v>45827.2810416667</x:v>
       </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="I9" s="20">
         <x:v>45827.2810648148</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="n">
+      <x:c r="J9" s="19" t="n">
         <x:v>1616</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="21" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="20">
         <x:v>45827.2917592593</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M9" s="19" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="B10" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s"/>
+      <x:c r="E10" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="H10" s="13">
         <x:v>45825.2634953704</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="13">
         <x:v>45825.2635300926</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="12" t="n">
         <x:v>274001</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="15">
         <x:v>45825.2871759259</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>23</x:v>
+      <x:c r="M10" s="11" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="B11" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s"/>
+      <x:c r="E11" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="I11" s="13">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="12" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="15">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>23</x:v>
+      <x:c r="M11" s="11" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
+      <x:c r="B14" s="22" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="24" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
-        <x:v>39</x:v>
+      <x:c r="B15" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="28" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="28" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="32" t="s"/>
+      <x:c r="D18" s="32" t="s"/>
+      <x:c r="E18" s="32" t="s"/>
+      <x:c r="F18" s="33" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>EXAM SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -901,7 +901,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45809</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1185,61 +1185,61 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="24" t="s"/>
     </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="25" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="28" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="31" t="s">
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="31" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
+      <x:c r="C20" s="32" t="s"/>
+      <x:c r="D20" s="32" t="s"/>
+      <x:c r="E20" s="32" t="s"/>
+      <x:c r="F20" s="33" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2214,14 +2214,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -512,7 +512,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -548,6 +548,50 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -567,28 +611,8 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -962,7 +986,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -1000,7 +1024,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>
@@ -1112,131 +1136,157 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+      <x:c r="B10" s="22" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="C10" s="22" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s"/>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="D10" s="23" t="s"/>
+      <x:c r="E10" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="F10" s="22" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="G10" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="H10" s="24">
         <x:v>45825.2634953704</x:v>
       </x:c>
-      <x:c r="I10" s="13">
+      <x:c r="I10" s="24">
         <x:v>45825.2635300926</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="23" t="n">
         <x:v>274001</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="25" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="26">
         <x:v>45825.2871759259</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
+      <x:c r="M10" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
+      <x:c r="B11" s="22" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="s">
+      <x:c r="C11" s="22" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s"/>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="D11" s="23" t="s"/>
+      <x:c r="E11" s="22" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="F11" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="G11" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="H11" s="24">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I11" s="13">
+      <x:c r="I11" s="24">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="23" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="25" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="26">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
+      <x:c r="M11" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B12" s="27" t="s"/>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="27" t="s"/>
+      <x:c r="G12" s="27" t="s"/>
+      <x:c r="H12" s="27" t="s"/>
+      <x:c r="I12" s="27" t="s"/>
+      <x:c r="J12" s="27" t="s"/>
+      <x:c r="K12" s="27" t="s"/>
+      <x:c r="L12" s="27" t="s"/>
+      <x:c r="M12" s="27" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B13" s="27" t="s"/>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="27" t="s"/>
+      <x:c r="G13" s="27" t="s"/>
+      <x:c r="H13" s="27" t="s"/>
+      <x:c r="I13" s="27" t="s"/>
+      <x:c r="J13" s="27" t="s"/>
+      <x:c r="K13" s="27" t="s"/>
+      <x:c r="L13" s="27" t="s"/>
+      <x:c r="M13" s="27" t="s"/>
+    </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="22" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="24" t="s"/>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="30" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="25" t="s">
+      <x:c r="B17" s="31" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="s">
+      <x:c r="C17" s="32" t="s"/>
+      <x:c r="D17" s="32" t="s"/>
+      <x:c r="E17" s="32" t="s"/>
+      <x:c r="F17" s="33" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
+      <x:c r="B18" s="34" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="35" t="s"/>
+      <x:c r="D18" s="35" t="s"/>
+      <x:c r="E18" s="35" t="s"/>
+      <x:c r="F18" s="36" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
+      <x:c r="B19" s="34" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="C19" s="35" t="s"/>
+      <x:c r="D19" s="35" t="s"/>
+      <x:c r="E19" s="35" t="s"/>
+      <x:c r="F19" s="36" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="31" t="s">
+      <x:c r="B20" s="37" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C20" s="32" t="s"/>
-      <x:c r="D20" s="32" t="s"/>
-      <x:c r="E20" s="32" t="s"/>
-      <x:c r="F20" s="33" t="n">
+      <x:c r="C20" s="38" t="s"/>
+      <x:c r="D20" s="38" t="s"/>
+      <x:c r="E20" s="38" t="s"/>
+      <x:c r="F20" s="39" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -956,7 +956,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1024,7 +1024,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,9 +22,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <x:si>
     <x:t>EXAM SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -118,7 +154,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -163,21 +199,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -187,6 +208,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -437,7 +465,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -448,71 +476,65 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="40">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -543,56 +565,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -607,59 +581,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -958,18 +944,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -987,306 +961,318 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45832.3384259259</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s"/>
-      <x:c r="E8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H8" s="20">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I8" s="20">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J8" s="19" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45832.3271759259</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45832.3271990741</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>16854</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>6</x:v>
+      <x:c r="L8" s="12">
+        <x:v>45832.3384259259</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s"/>
-      <x:c r="E9" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I9" s="20">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J9" s="19" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="20">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>6</x:v>
+      <x:c r="L9" s="12">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="22" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="22" t="s">
+      <x:c r="B10" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="D10" s="23" t="s"/>
-      <x:c r="E10" s="22" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H10" s="24">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I10" s="24">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J10" s="23" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K10" s="25" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L10" s="26">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M10" s="22" t="s">
-        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="22" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D11" s="23" t="s"/>
-      <x:c r="E11" s="22" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F11" s="22" t="s">
+      <x:c r="B11" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G11" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H11" s="24">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I11" s="24">
+      <x:c r="I13" s="16">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J11" s="23" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K11" s="25" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="26">
+      <x:c r="L13" s="18">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M11" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="27" t="s"/>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="27" t="s"/>
-      <x:c r="G12" s="27" t="s"/>
-      <x:c r="H12" s="27" t="s"/>
-      <x:c r="I12" s="27" t="s"/>
-      <x:c r="J12" s="27" t="s"/>
-      <x:c r="K12" s="27" t="s"/>
-      <x:c r="L12" s="27" t="s"/>
-      <x:c r="M12" s="27" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B13" s="27" t="s"/>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="27" t="s"/>
-      <x:c r="G13" s="27" t="s"/>
-      <x:c r="H13" s="27" t="s"/>
-      <x:c r="I13" s="27" t="s"/>
-      <x:c r="J13" s="27" t="s"/>
-      <x:c r="K13" s="27" t="s"/>
-      <x:c r="L13" s="27" t="s"/>
-      <x:c r="M13" s="27" t="s"/>
+      <x:c r="M13" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="30" t="s"/>
+      <x:c r="B16" s="19" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="31" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C17" s="32" t="s"/>
-      <x:c r="D17" s="32" t="s"/>
-      <x:c r="E17" s="32" t="s"/>
-      <x:c r="F17" s="33" t="s">
-        <x:v>27</x:v>
+      <x:c r="B17" s="22" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="35" t="s"/>
-      <x:c r="D18" s="35" t="s"/>
-      <x:c r="E18" s="35" t="s"/>
-      <x:c r="F18" s="36" t="n">
+      <x:c r="B18" s="25" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="34" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C19" s="35" t="s"/>
-      <x:c r="D19" s="35" t="s"/>
-      <x:c r="E19" s="35" t="s"/>
-      <x:c r="F19" s="36" t="n">
+      <x:c r="B19" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="37" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C20" s="38" t="s"/>
-      <x:c r="D20" s="38" t="s"/>
-      <x:c r="E20" s="38" t="s"/>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="B20" s="28" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -465,11 +465,14 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -534,7 +537,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -564,6 +567,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -894,7 +901,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45809</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -966,313 +975,313 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45832.3271759259</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>45832.3271990741</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>16854</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45832.3384259259</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="12" t="s"/>
+      <x:c r="E9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45826.3053472222</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>45826.3053703704</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1434444</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45826.3117939815</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="H10" s="17">
         <x:v>45825.0450347222</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="17">
         <x:v>45825.0450578704</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1546810</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45825.0561574074</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="C11" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="H11" s="17">
         <x:v>45827.2810416667</x:v>
       </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="I11" s="17">
         <x:v>45827.2810648148</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1616</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>45827.2917592593</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
+      <x:c r="M11" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="B12" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="C12" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="H12" s="17">
         <x:v>45825.2634953704</x:v>
       </x:c>
-      <x:c r="I12" s="16">
+      <x:c r="I12" s="17">
         <x:v>45825.2635300926</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>274001</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>45825.2871759259</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
+      <x:c r="M12" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="B13" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="C13" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s"/>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="H13" s="17">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I13" s="16">
+      <x:c r="I13" s="17">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
+      <x:c r="M13" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="19" t="s">
+      <x:c r="B16" s="20" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="21" t="s"/>
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="22" t="s">
+      <x:c r="B17" s="23" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="s">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
+      <x:c r="B18" s="26" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
+      <x:c r="B19" s="26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="28" t="s">
+      <x:c r="B20" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,9 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <x:si>
-    <x:t>EXAM SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+  <x:si>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXAMS SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -154,7 +160,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -194,6 +200,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -465,17 +495,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -488,56 +524,56 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -568,91 +604,99 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -881,58 +925,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45809</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -975,313 +1019,313 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="F8" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45832.3271759259</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>45832.3271990741</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>16854</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45832.3384259259</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s"/>
-      <x:c r="E9" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="s">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="F9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45826.3053472222</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="15">
         <x:v>45826.3053703704</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1434444</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>45826.3117939815</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>23</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="B12" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>45825.2634953704</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="19">
         <x:v>45825.2635300926</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>274001</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="20" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="21">
         <x:v>45825.2871759259</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M12" s="17" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="B13" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="17" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="F13" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="19">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="20" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="21">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>23</x:v>
+      <x:c r="M13" s="17" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+      <x:c r="B16" s="22" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="24" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
-        <x:v>39</x:v>
+      <x:c r="B17" s="25" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="B19" s="28" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
+      <x:c r="B20" s="31" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C20" s="32" t="s"/>
+      <x:c r="D20" s="32" t="s"/>
+      <x:c r="E20" s="32" t="s"/>
+      <x:c r="F20" s="33" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2262,7 +2306,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -67,6 +67,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -157,10 +193,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -205,15 +243,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -229,15 +259,8 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -495,26 +518,26 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -524,56 +547,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -604,99 +630,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -925,78 +943,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1017,7 +1047,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1057,280 +1087,330 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45832.3384259259</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
       <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="B10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45832.3271759259</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45832.3271990741</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>16854</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L10" s="19">
+        <x:v>45832.3384259259</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="B11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L11" s="19">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
+      <x:c r="B13" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s"/>
+      <x:c r="E14" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s"/>
+      <x:c r="E15" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="I15" s="17">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J13" s="18" t="n">
+      <x:c r="J15" s="16" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L13" s="21">
+      <x:c r="L15" s="19">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="M15" s="15" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="24" t="s"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="20" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
     </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="25" t="s">
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="23" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="s">
-        <x:v>41</x:v>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
-        <x:v>3</x:v>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="29" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="31" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C20" s="32" t="s"/>
-      <x:c r="D20" s="32" t="s"/>
-      <x:c r="E20" s="32" t="s"/>
-      <x:c r="F20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2303,15 +2383,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="9">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -67,42 +67,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -198,7 +162,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -242,14 +206,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -261,6 +217,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -518,7 +489,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -526,16 +497,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -547,13 +518,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -565,41 +530,50 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -630,28 +604,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -666,55 +632,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1047,7 +1029,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1087,330 +1069,280 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45832.3271759259</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45832.3271990741</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>16854</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45832.3384259259</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="H9" s="15">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s"/>
+      <x:c r="E10" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="H10" s="19">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45832.3384259259</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="L10" s="21">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="B11" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>37</x:v>
+      <x:c r="L11" s="21">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="B12" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="G12" s="17" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="H12" s="19">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="L12" s="21">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>45826.3109259259</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>45826.3109375</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1432235</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>45826.3168865741</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="22" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="24" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="25" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="28" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="31" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>32</x:v>
+      <x:c r="C20" s="32" t="s"/>
+      <x:c r="D20" s="32" t="s"/>
+      <x:c r="E20" s="32" t="s"/>
+      <x:c r="F20" s="33" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="29" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C22" s="30" t="s"/>
-      <x:c r="D22" s="30" t="s"/>
-      <x:c r="E22" s="30" t="s"/>
-      <x:c r="F22" s="31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2388,11 +2320,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B18:F18"/>
+    <x:mergeCell ref="B16:F16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -84,6 +84,9 @@
     <x:t>61-6-2025-1061</x:t>
   </x:si>
   <x:si>
+    <x:t>16854</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier3 edge</x:t>
   </x:si>
   <x:si>
@@ -99,6 +102,9 @@
     <x:t>61-6-2025-1023</x:t>
   </x:si>
   <x:si>
+    <x:t>1434444</x:t>
+  </x:si>
+  <x:si>
     <x:t>MANUELITO TOLENTINO</x:t>
   </x:si>
   <x:si>
@@ -108,6 +114,9 @@
     <x:t>61-6-2025-1003</x:t>
   </x:si>
   <x:si>
+    <x:t>1546810</x:t>
+  </x:si>
+  <x:si>
     <x:t>Radiotelegraphy</x:t>
   </x:si>
   <x:si>
@@ -120,6 +129,9 @@
     <x:t>61-6-2025-1054</x:t>
   </x:si>
   <x:si>
+    <x:t>1616</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANGELICA VERGARA PANCHITO</x:t>
   </x:si>
   <x:si>
@@ -129,6 +141,9 @@
     <x:t>61-6-2025-1007</x:t>
   </x:si>
   <x:si>
+    <x:t>274001</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWARD LANCE LORILLA</x:t>
   </x:si>
   <x:si>
@@ -139,6 +154,9 @@
   </x:si>
   <x:si>
     <x:t>61-6-2025-1025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1432235</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -162,7 +180,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -231,13 +249,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -489,7 +500,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -530,50 +541,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -621,6 +623,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -632,71 +638,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1077,7 +1067,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1087,23 +1077,23 @@
       <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>45832.3271846875</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45832.3272087963</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45832.3384259259</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45832.3384320023</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1111,233 +1101,233 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45826.3053530208</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45826.3053769676</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45826.3117939815</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45826.311800463</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45825.0450396991</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45825.0450687153</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>45825.0561645718</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="C11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45827.2810495602</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>45827.2810737963</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>20</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45827.2917648032</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="B12" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45825.2635056481</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>45825.2635335069</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="L12" s="18">
+        <x:v>45825.2871799306</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="B13" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45826.310926169</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>45826.3109462384</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="L13" s="18">
+        <x:v>45826.3168925232</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="24" t="s"/>
+      <x:c r="B16" s="19" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="s">
-        <x:v>41</x:v>
+      <x:c r="B17" s="22" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="25" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="31" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C20" s="32" t="s"/>
-      <x:c r="D20" s="32" t="s"/>
-      <x:c r="E20" s="32" t="s"/>
-      <x:c r="F20" s="33" t="n">
+      <x:c r="B20" s="28" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -1019,7 +1019,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1059,7 +1059,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1096,7 +1096,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1132,7 +1132,7 @@
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1168,7 +1168,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
@@ -1204,7 +1204,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
@@ -1240,7 +1240,7 @@
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>31</x:v>
       </x:c>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,15 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
   <x:si>
     <x:t>EXAMS SUMMARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -500,7 +497,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -517,6 +514,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -575,7 +575,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -611,6 +611,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -985,20 +989,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45809</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1021,313 +1025,313 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45832.3271846875</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45832.3272087963</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45832.3271846875</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45832.3272087963</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45832.3384320023</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45832.3384320023</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45826.3053530208</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45826.3053769676</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45826.3053530208</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45826.3053769676</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45826.311800463</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45826.311800463</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45825.0450396991</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45825.0450687153</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45825.0450396991</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45825.0450687153</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45825.0561645718</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>45827.2810495602</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45827.2810737963</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45827.2810495602</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45827.2810737963</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>45827.2917648032</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="17">
+        <x:v>45825.2635056481</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45825.2635335069</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45825.2635056481</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45825.2635335069</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>45825.2871799306</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>27</x:v>
+      <x:c r="M12" s="15" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="B13" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s"/>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="H13" s="17">
+        <x:v>45826.310926169</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45826.3109462384</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45826.310926169</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45826.3109462384</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>45826.3168925232</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>27</x:v>
+      <x:c r="M13" s="15" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="19" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="21" t="s"/>
+      <x:c r="B16" s="20" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="22" t="s">
+      <x:c r="B17" s="23" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
+      <x:c r="B19" s="26" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="28" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="B20" s="29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -177,7 +177,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -217,14 +217,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -497,7 +489,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -508,16 +500,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -529,53 +518,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -610,87 +599,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -992,17 +977,17 @@
       <x:c r="B5" s="12">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1025,313 +1010,313 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45832.3271846875</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45832.3272087963</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45832.3384320023</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45826.3053530208</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45826.3053769676</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45826.311800463</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45825.0450396991</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45825.0450687153</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45825.0561645718</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45827.2810495602</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45827.2810737963</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45827.2917648032</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45825.2635056481</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45825.2635335069</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45825.2871799306</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45826.310926169</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45826.3109462384</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45826.3168925232</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+      <x:c r="B16" s="19" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
+      <x:c r="B20" s="28" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-exam_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -69,6 +69,78 @@
     <x:t>Amateur</x:t>
   </x:si>
   <x:si>
+    <x:t>JULIETA ROBLEDO AMANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1003-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1546810</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cashier3 edge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radiotelegraphy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGELICA VERGARA PANCHITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1007-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>274001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANUELITO TOLENTINO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1018-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1434444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDWARD LANCE LORILLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sarphil subdivision RN Pelaez BLVD Kauwagan, 1, Abucay, Bataan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1020-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1432235</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEL PANCHITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1021-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1054</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1616</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDISSA ABASTAS AMANTE</x:t>
   </x:si>
   <x:si>
@@ -82,78 +154,6 @@
   </x:si>
   <x:si>
     <x:t>16854</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cashier3 edge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JULIETA ROBLEDO AMANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1018-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1434444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANUELITO TOLENTINO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1003-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1546810</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Radiotelegraphy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEL PANCHITO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1021-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1054</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1616</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGELICA VERGARA PANCHITO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1007-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>274001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDWARD LANCE LORILLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sarphil subdivision RN Pelaez BLVD Kauwagan, 1, Abucay, Bataan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1020-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1432235</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -1067,10 +1067,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>45832.3271846875</x:v>
+        <x:v>45825.0450396991</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>45832.3272087963</x:v>
+        <x:v>45825.0450687153</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
@@ -1079,7 +1079,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>45832.3384320023</x:v>
+        <x:v>45825.0561645718</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
@@ -1087,14 +1087,14 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
@@ -1103,10 +1103,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>45826.3053530208</x:v>
+        <x:v>45825.2635056481</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>45826.3053769676</x:v>
+        <x:v>45825.2635335069</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
@@ -1115,7 +1115,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>45826.311800463</x:v>
+        <x:v>45825.2871799306</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>26</x:v>
@@ -1126,11 +1126,11 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
         <x:v>27</x:v>
@@ -1139,10 +1139,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>45825.0450396991</x:v>
+        <x:v>45826.3053530208</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>45825.0450687153</x:v>
+        <x:v>45826.3053769676</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>29</x:v>
@@ -1151,22 +1151,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>45825.0561645718</x:v>
+        <x:v>45826.311800463</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s"/>
       <x:c r="E11" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
         <x:v>32</x:v>
@@ -1175,10 +1175,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>45827.2810495602</x:v>
+        <x:v>45826.310926169</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>45827.2810737963</x:v>
+        <x:v>45826.3109462384</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>34</x:v>
@@ -1187,22 +1187,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>45827.2917648032</x:v>
+        <x:v>45826.3168925232</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s"/>
       <x:c r="E12" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
         <x:v>36</x:v>
@@ -1211,10 +1211,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>45825.2635056481</x:v>
+        <x:v>45827.2810495602</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>45825.2635335069</x:v>
+        <x:v>45827.2810737963</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>38</x:v>
@@ -1223,15 +1223,15 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>45825.2871799306</x:v>
+        <x:v>45827.2917648032</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
         <x:v>39</x:v>
@@ -1247,10 +1247,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>45826.310926169</x:v>
+        <x:v>45832.3271846875</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>45826.3109462384</x:v>
+        <x:v>45832.3272087963</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>43</x:v>
@@ -1259,10 +1259,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>45826.3168925232</x:v>
+        <x:v>45832.3384320023</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
@@ -1300,7 +1300,7 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="25" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="26" t="s"/>
       <x:c r="D19" s="26" t="s"/>
